--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B109"/>
+  <dimension ref="A1:B110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1477,6 +1477,16 @@
         <v>154908</v>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>152475</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B110"/>
+  <dimension ref="A1:B111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1487,6 +1487,16 @@
         <v>152475</v>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>153309</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B111"/>
+  <dimension ref="A1:B112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1497,6 +1497,16 @@
         <v>153309</v>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>153432</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B112"/>
+  <dimension ref="A1:B113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1507,6 +1507,16 @@
         <v>153432</v>
       </c>
     </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>154028</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B113"/>
+  <dimension ref="A1:B114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1517,6 +1517,16 @@
         <v>154028</v>
       </c>
     </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>153018</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B114"/>
+  <dimension ref="A1:B115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1527,6 +1527,16 @@
         <v>153018</v>
       </c>
     </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>151050</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B115"/>
+  <dimension ref="A1:B116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1537,6 +1537,16 @@
         <v>151050</v>
       </c>
     </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>151894</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B116"/>
+  <dimension ref="A1:B117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1547,6 +1547,16 @@
         <v>151894</v>
       </c>
     </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>151233</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B117"/>
+  <dimension ref="A1:B118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1557,6 +1557,16 @@
         <v>151233</v>
       </c>
     </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>153658</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B118"/>
+  <dimension ref="A1:B119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1567,6 +1567,16 @@
         <v>153658</v>
       </c>
     </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>152132</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B119"/>
+  <dimension ref="A1:B120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1577,6 +1577,16 @@
         <v>152132</v>
       </c>
     </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>152266</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B120"/>
+  <dimension ref="A1:B121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1587,6 +1587,16 @@
         <v>152266</v>
       </c>
     </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>151163</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B121"/>
+  <dimension ref="A1:B122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1597,6 +1597,16 @@
         <v>151163</v>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>151136</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B122"/>
+  <dimension ref="A1:B123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1607,6 +1607,16 @@
         <v>151136</v>
       </c>
     </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>148048</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B123"/>
+  <dimension ref="A1:B124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1617,6 +1617,16 @@
         <v>148048</v>
       </c>
     </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>147400</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B124"/>
+  <dimension ref="A1:B125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1627,6 +1627,16 @@
         <v>147400</v>
       </c>
     </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>148379</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B125"/>
+  <dimension ref="A1:B126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1637,6 +1637,16 @@
         <v>148379</v>
       </c>
     </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>148687</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B126"/>
+  <dimension ref="A1:B127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1647,6 +1647,16 @@
         <v>148687</v>
       </c>
     </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>147785</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B127"/>
+  <dimension ref="A1:B128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1657,6 +1657,16 @@
         <v>147785</v>
       </c>
     </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>147278</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B128"/>
+  <dimension ref="A1:B129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1667,6 +1667,16 @@
         <v>147278</v>
       </c>
     </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>147975</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B129"/>
+  <dimension ref="A1:B130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1677,6 +1677,16 @@
         <v>147975</v>
       </c>
     </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>147463</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B130"/>
+  <dimension ref="A1:B131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1687,6 +1687,16 @@
         <v>147463</v>
       </c>
     </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>149614</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B131"/>
+  <dimension ref="A1:B132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1697,6 +1697,16 @@
         <v>149614</v>
       </c>
     </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>148425</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B132"/>
+  <dimension ref="A1:B133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1707,6 +1707,16 @@
         <v>148425</v>
       </c>
     </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>147662</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B133"/>
+  <dimension ref="A1:B134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1717,6 +1717,16 @@
         <v>147662</v>
       </c>
     </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>146345</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B134"/>
+  <dimension ref="A1:B135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1727,6 +1727,16 @@
         <v>146345</v>
       </c>
     </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>145564</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B135"/>
+  <dimension ref="A1:B136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1737,6 +1737,16 @@
         <v>145564</v>
       </c>
     </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>146514</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B136"/>
+  <dimension ref="A1:B137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1747,6 +1747,16 @@
         <v>146514</v>
       </c>
     </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>146406</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B137"/>
+  <dimension ref="A1:B138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1757,6 +1757,16 @@
         <v>146406</v>
       </c>
     </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>144060</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B138"/>
+  <dimension ref="A1:B139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1767,6 +1767,16 @@
         <v>144060</v>
       </c>
     </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>143152</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B139"/>
+  <dimension ref="A1:B140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1777,6 +1777,16 @@
         <v>143152</v>
       </c>
     </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>141448</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B140"/>
+  <dimension ref="A1:B141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1787,6 +1787,16 @@
         <v>141448</v>
       </c>
     </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>141290</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B141"/>
+  <dimension ref="A1:B142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1797,6 +1797,16 @@
         <v>141290</v>
       </c>
     </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>141082</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B142"/>
+  <dimension ref="A1:B143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1807,6 +1807,16 @@
         <v>141082</v>
       </c>
     </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>142300</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B143"/>
+  <dimension ref="A1:B144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1817,6 +1817,16 @@
         <v>142300</v>
       </c>
     </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>142144</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B144"/>
+  <dimension ref="A1:B145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1827,6 +1827,16 @@
         <v>142144</v>
       </c>
     </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>140891</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
